--- a/data/trans_dic/IP16A09-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A09-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos</t>
+          <t>Menores que consumiero medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,56</t>
+          <t>0,0; 32,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,72</t>
+          <t>0,0; 13,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,93</t>
+          <t>0,0; 14,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,02</t>
+          <t>0,0; 24,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 19,96</t>
+          <t>2,15; 20,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,98</t>
+          <t>0,0; 5,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,22</t>
+          <t>0,0; 6,34</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,81</t>
+          <t>0,0; 20,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,68</t>
+          <t>0,0; 12,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 23,27</t>
+          <t>0,0; 23,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,92</t>
+          <t>0,0; 10,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 28,74</t>
+          <t>5,66; 28,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 15,64</t>
+          <t>1,72; 14,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,28</t>
+          <t>0,89; 8,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 12,77</t>
+          <t>1,32; 11,95</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,44</t>
+          <t>0,0; 23,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,78</t>
+          <t>0,0; 14,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,06</t>
+          <t>0,0; 10,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,93</t>
+          <t>0,0; 20,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,19</t>
+          <t>0,0; 12,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,87</t>
+          <t>0,0; 11,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,21</t>
+          <t>0,0; 6,2</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,9</t>
+          <t>0,0; 19,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,28</t>
+          <t>0,0; 9,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,49</t>
+          <t>0,0; 15,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,18</t>
+          <t>0,0; 14,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,67</t>
+          <t>0,0; 16,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,45</t>
+          <t>0,0; 12,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,76</t>
+          <t>0,0; 13,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,66</t>
+          <t>0,0; 10,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 9,81</t>
+          <t>1,04; 9,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,43</t>
+          <t>0,0; 9,37</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,74; 20,63</t>
+          <t>1,71; 19,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 3,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 3,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,46</t>
+          <t>0,0; 19,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 7,39</t>
+          <t>0,68; 8,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,67</t>
+          <t>0,0; 10,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,02; 7,96</t>
+          <t>1,81; 7,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,15</t>
+          <t>0,61; 4,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,66</t>
+          <t>0,35; 3,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,15</t>
+          <t>0,9; 5,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,6</t>
+          <t>1,38; 5,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,67</t>
+          <t>0,47; 4,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,94</t>
+          <t>1,82; 5,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,08</t>
+          <t>1,35; 4,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,14</t>
+          <t>0,72; 2,88</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1719</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3779</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2641</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2760</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2961</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>511; 4881</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2599</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2794</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1272</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1937</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2550</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2508</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3434</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3989</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4614</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3784</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1319; 6754</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>629; 5317</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>628; 5692</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>710; 6421</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1531</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4439</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3454</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4683</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1124</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1124</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3286</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4268</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3789</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4003</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2696</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3320</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2260</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3332</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4907</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3187</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3283</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4070</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4904</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>649; 6231</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3157</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>1838</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1838</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>444; 4962</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0; 5320</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>449; 5668</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 5511</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>5197</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>3501</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2277</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>5582</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>8469</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>9083</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>5075</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>2266; 9194</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>1138; 8671</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>567; 5130</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1292; 7784</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2640; 10605</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>703; 6388</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>4898; 14346</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>5103; 15211</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>2245; 8960</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A09-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A09-Provincia-trans_dic.xlsx
@@ -678,22 +678,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,39</t>
+          <t>0,0; 23,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,86</t>
+          <t>0,0; 14,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,11</t>
+          <t>0,0; 13,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,4</t>
+          <t>0,0; 29,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 20,51</t>
+          <t>2,13; 19,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,95</t>
+          <t>0,0; 5,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,34</t>
+          <t>0,0; 5,96</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,53</t>
+          <t>0,0; 18,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,11</t>
+          <t>0,0; 13,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,32 +803,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,24</t>
+          <t>3,12; 23,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,15</t>
+          <t>0,0; 12,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 28,97</t>
+          <t>3,02; 26,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 14,53</t>
+          <t>1,81; 15,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,1</t>
+          <t>0,89; 8,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 11,95</t>
+          <t>1,3; 12,18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,03</t>
+          <t>0,0; 17,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,6</t>
+          <t>0,0; 13,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,91</t>
+          <t>0,0; 12,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,1</t>
+          <t>0,0; 22,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,22</t>
+          <t>0,0; 11,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,56</t>
+          <t>0,0; 11,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,2</t>
+          <t>0,0; 6,07</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,84</t>
+          <t>0,0; 25,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,94</t>
+          <t>0,0; 11,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1338,27 +1338,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,5</t>
+          <t>0,0; 15,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,64</t>
+          <t>0,0; 13,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,16</t>
+          <t>0,0; 15,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,38</t>
+          <t>0,0; 14,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,94</t>
+          <t>0,0; 14,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,21</t>
+          <t>0,0; 8,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,94</t>
+          <t>1,05; 10,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,37</t>
+          <t>0,0; 9,1</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,71; 19,14</t>
+          <t>1,73; 17,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,77</t>
+          <t>0,0; 20,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 8,62</t>
+          <t>0,68; 7,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,75</t>
+          <t>0,0; 9,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,81; 7,34</t>
+          <t>1,9; 7,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,64</t>
+          <t>0,66; 4,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,16</t>
+          <t>0,35; 3,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,41</t>
+          <t>0,9; 5,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,38; 5,54</t>
+          <t>1,3; 5,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,31</t>
+          <t>0,48; 4,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,33</t>
+          <t>1,79; 5,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,02</t>
+          <t>1,29; 3,91</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,88</t>
+          <t>0,77; 3,18</t>
         </is>
       </c>
     </row>
@@ -1861,22 +1861,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3779</t>
+          <t>0; 2782</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2641</t>
+          <t>0; 2696</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2760</t>
+          <t>0; 2676</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2961</t>
+          <t>0; 3537</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>511; 4881</t>
+          <t>507; 4628</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2599</t>
+          <t>0; 2545</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2794</t>
+          <t>0; 2625</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3434</t>
+          <t>0; 3059</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3989</t>
+          <t>0; 4551</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2039,32 +2039,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4614</t>
+          <t>620; 4681</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3784</t>
+          <t>0; 4510</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1319; 6754</t>
+          <t>705; 6077</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>629; 5317</t>
+          <t>661; 5749</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>628; 5692</t>
+          <t>626; 5775</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>710; 6421</t>
+          <t>701; 6546</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4439</t>
+          <t>0; 3311</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3454</t>
+          <t>0; 3256</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4683</t>
+          <t>0; 5297</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3286</t>
+          <t>0; 3680</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4268</t>
+          <t>0; 4179</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3789</t>
+          <t>0; 3714</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4003</t>
+          <t>0; 3914</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2696</t>
+          <t>0; 3407</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3320</t>
+          <t>0; 3935</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2839,27 +2839,27 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3332</t>
+          <t>0; 3315</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4907</t>
+          <t>0; 4595</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3187</t>
+          <t>0; 3102</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3283</t>
+          <t>0; 3833</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4070</t>
+          <t>0; 4183</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2869,17 +2869,17 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 4904</t>
+          <t>0; 3985</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>649; 6231</t>
+          <t>656; 6422</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 3157</t>
+          <t>0; 3065</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>444; 4962</t>
+          <t>448; 4530</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 5320</t>
+          <t>0; 5569</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>449; 5668</t>
+          <t>447; 5202</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 5511</t>
+          <t>0; 4899</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2266; 9194</t>
+          <t>2376; 9439</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1138; 8671</t>
+          <t>1233; 7573</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>567; 5130</t>
+          <t>570; 5852</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1292; 7784</t>
+          <t>1288; 7196</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2640; 10605</t>
+          <t>2493; 10500</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>703; 6388</t>
+          <t>707; 7017</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4898; 14346</t>
+          <t>4821; 13572</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5103; 15211</t>
+          <t>4866; 14812</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2245; 8960</t>
+          <t>2391; 9879</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A09-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A09-Provincia-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>8,86%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2,61%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,76%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,84</t>
+          <t>0,0; 29,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,15</t>
+          <t>0,0; 27,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 12,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 11,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 19,44</t>
+          <t>2,12; 19,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,83</t>
+          <t>0,0; 5,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,96</t>
+          <t>0,0; 7,22</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>3,66%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>3,86%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9,75%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,29</t>
+          <t>3,16; 23,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,81</t>
+          <t>0,0; 11,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,12; 28,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 23,57</t>
+          <t>0,0; 20,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,09</t>
+          <t>0,0; 13,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 26,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 15,71</t>
+          <t>1,76; 15,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,22</t>
+          <t>0,89; 8,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 12,18</t>
+          <t>1,32; 12,77</t>
         </is>
       </c>
     </row>
@@ -850,22 +850,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4,08%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,17</t>
+          <t>0,0; 12,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,76</t>
+          <t>0,0; 17,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,34</t>
+          <t>0,0; 11,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>6,4%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,22%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 20,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 11,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,33</t>
+          <t>0,0; 9,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,07</t>
+          <t>0,0; 6,21</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 24,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,78</t>
+          <t>0,0; 11,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>3,1%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,82%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3,11%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,42</t>
+          <t>0,0; 12,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,71</t>
+          <t>0,0; 13,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,45</t>
+          <t>0,0; 14,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,33</t>
+          <t>0,0; 16,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 15,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,3</t>
+          <t>0,0; 9,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 10,24</t>
+          <t>1,03; 9,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,1</t>
+          <t>0,0; 10,43</t>
         </is>
       </c>
     </row>
@@ -1395,27 +1395,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>7,09%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,73; 17,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 18,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,74; 20,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 7,91</t>
+          <t>0,68; 7,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,56</t>
+          <t>0,0; 10,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>4,15%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1,87%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,53</t>
+          <t>0,89; 5,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,05</t>
+          <t>1,36; 5,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,6</t>
+          <t>0,48; 4,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,0</t>
+          <t>2,02; 7,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,48</t>
+          <t>0,68; 4,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,74</t>
+          <t>0,35; 3,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,04</t>
+          <t>1,69; 4,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,91</t>
+          <t>1,35; 4,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,18</t>
+          <t>0,74; 3,14</t>
         </is>
       </c>
     </row>
@@ -1654,20 +1654,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,32 +1755,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1034</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>498</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>540</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2782</t>
+          <t>0; 3522</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2696</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2676</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3537</t>
+          <t>0; 3216</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2424</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2332</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>507; 4628</t>
+          <t>505; 4752</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2545</t>
+          <t>0; 2608</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2625</t>
+          <t>0; 3182</t>
         </is>
       </c>
     </row>
@@ -1918,32 +1918,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1937</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>613</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1272</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1937</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1235</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3059</t>
+          <t>628; 4620</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4551</t>
+          <t>0; 4445</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>727; 6701</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>620; 4681</t>
+          <t>0; 3482</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4510</t>
+          <t>0; 4508</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>705; 6077</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>661; 5749</t>
+          <t>642; 5723</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>626; 5775</t>
+          <t>627; 5817</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>701; 6546</t>
+          <t>710; 6859</t>
         </is>
       </c>
     </row>
@@ -2139,22 +2139,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>787</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>744</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3311</t>
+          <t>0; 3023</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3256</t>
+          <t>0; 3362</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5297</t>
+          <t>0; 4749</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2244,32 +2244,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1047</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1124</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3680</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4179</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3422</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3906</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3714</t>
+          <t>0; 3234</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3914</t>
+          <t>0; 4006</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>647</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3384</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3407</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3935</t>
+          <t>0; 3767</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2738,27 +2738,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>665</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>613</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3315</t>
+          <t>0; 3303</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4595</t>
+          <t>0; 4016</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3102</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3833</t>
+          <t>0; 3115</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4183</t>
+          <t>0; 5423</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3089</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3985</t>
+          <t>0; 4640</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>656; 6422</t>
+          <t>645; 6153</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 3065</t>
+          <t>0; 3511</t>
         </is>
       </c>
     </row>
@@ -2896,27 +2896,27 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2949,27 +2949,27 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>1838</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>448; 4530</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4967</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>452; 5348</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 5569</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>447; 5202</t>
+          <t>447; 4864</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4899</t>
+          <t>0; 5468</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -3059,27 +3059,27 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>5582</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>5197</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>3501</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>2277</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>3272</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>5582</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>2799</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2376; 9439</t>
+          <t>1282; 7416</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1233; 7573</t>
+          <t>2611; 10721</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>570; 5852</t>
+          <t>705; 6921</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1288; 7196</t>
+          <t>2528; 9976</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2493; 10500</t>
+          <t>1267; 7769</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>707; 7017</t>
+          <t>571; 5948</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4821; 13572</t>
+          <t>4546; 13313</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>4866; 14812</t>
+          <t>5106; 15444</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2391; 9879</t>
+          <t>2305; 9767</t>
         </is>
       </c>
     </row>
